--- a/outputs/Sugar_tukey_classification_matrix.xlsx
+++ b/outputs/Sugar_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="110">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,58 +343,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>18%</t>
   </si>
 </sst>
 </file>
@@ -1120,22 +1069,22 @@
         <v>108</v>
       </c>
       <c r="AM2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS2" t="s">
         <v>108</v>
@@ -1222,13 +1171,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV2" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1344,25 +1293,25 @@
         <v>108</v>
       </c>
       <c r="AL3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN3" t="s">
         <v>108</v>
       </c>
       <c r="AO3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS3" t="s">
         <v>108</v>
@@ -1371,7 +1320,7 @@
         <v>108</v>
       </c>
       <c r="AU3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV3" t="s">
         <v>108</v>
@@ -1449,13 +1398,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1571,19 +1520,19 @@
         <v>108</v>
       </c>
       <c r="AL4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ4" t="s">
         <v>108</v>
@@ -1676,13 +1625,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1771,7 +1720,7 @@
         <v>108</v>
       </c>
       <c r="AC5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD5" t="s">
         <v>108</v>
@@ -1798,22 +1747,22 @@
         <v>108</v>
       </c>
       <c r="AL5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR5" t="s">
         <v>108</v>
@@ -1903,13 +1852,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV5" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1992,19 +1941,19 @@
         <v>108</v>
       </c>
       <c r="AA6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s">
         <v>108</v>
@@ -2031,19 +1980,19 @@
         <v>108</v>
       </c>
       <c r="AN6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS6" t="s">
         <v>108</v>
@@ -2130,13 +2079,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2267,7 +2216,7 @@
         <v>108</v>
       </c>
       <c r="AQ7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR7" t="s">
         <v>108</v>
@@ -2357,13 +2306,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV7" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW7" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2449,7 +2398,7 @@
         <v>108</v>
       </c>
       <c r="AB8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC8" t="s">
         <v>108</v>
@@ -2479,7 +2428,7 @@
         <v>108</v>
       </c>
       <c r="AL8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM8" t="s">
         <v>108</v>
@@ -2491,7 +2440,7 @@
         <v>108</v>
       </c>
       <c r="AP8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ8" t="s">
         <v>108</v>
@@ -2584,13 +2533,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV8" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW8" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2679,7 +2628,7 @@
         <v>108</v>
       </c>
       <c r="AC9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD9" t="s">
         <v>108</v>
@@ -2706,25 +2655,25 @@
         <v>108</v>
       </c>
       <c r="AL9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN9" t="s">
         <v>108</v>
       </c>
       <c r="AO9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP9" t="s">
         <v>108</v>
       </c>
       <c r="AQ9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS9" t="s">
         <v>108</v>
@@ -2733,13 +2682,13 @@
         <v>108</v>
       </c>
       <c r="AU9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX9" t="s">
         <v>108</v>
@@ -2811,13 +2760,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV9" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW9" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2903,10 +2852,10 @@
         <v>108</v>
       </c>
       <c r="AB10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD10" t="s">
         <v>108</v>
@@ -2933,37 +2882,37 @@
         <v>108</v>
       </c>
       <c r="AL10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT10" t="s">
         <v>108</v>
       </c>
       <c r="AU10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW10" t="s">
         <v>108</v>
@@ -3038,13 +2987,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV10" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW10" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3160,10 +3109,10 @@
         <v>108</v>
       </c>
       <c r="AL11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN11" t="s">
         <v>108</v>
@@ -3178,7 +3127,7 @@
         <v>108</v>
       </c>
       <c r="AR11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS11" t="s">
         <v>108</v>
@@ -3187,7 +3136,7 @@
         <v>108</v>
       </c>
       <c r="AU11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV11" t="s">
         <v>108</v>
@@ -3265,13 +3214,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3357,7 +3306,7 @@
         <v>108</v>
       </c>
       <c r="AB12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC12" t="s">
         <v>108</v>
@@ -3387,34 +3336,34 @@
         <v>108</v>
       </c>
       <c r="AL12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS12" t="s">
         <v>108</v>
       </c>
       <c r="AT12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV12" t="s">
         <v>108</v>
@@ -3492,13 +3441,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV12" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3590,7 +3539,7 @@
         <v>108</v>
       </c>
       <c r="AD13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE13" t="s">
         <v>108</v>
@@ -3614,34 +3563,34 @@
         <v>108</v>
       </c>
       <c r="AL13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT13" t="s">
         <v>108</v>
       </c>
       <c r="AU13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV13" t="s">
         <v>108</v>
@@ -3719,13 +3668,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV13" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3811,10 +3760,10 @@
         <v>108</v>
       </c>
       <c r="AB14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD14" t="s">
         <v>108</v>
@@ -3841,22 +3790,22 @@
         <v>108</v>
       </c>
       <c r="AL14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR14" t="s">
         <v>108</v>
@@ -3868,7 +3817,7 @@
         <v>108</v>
       </c>
       <c r="AU14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV14" t="s">
         <v>108</v>
@@ -3946,13 +3895,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV14" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW14" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4068,25 +4017,25 @@
         <v>108</v>
       </c>
       <c r="AL15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ15" t="s">
         <v>108</v>
       </c>
       <c r="AR15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS15" t="s">
         <v>108</v>
@@ -4173,13 +4122,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV15" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4247,7 +4196,7 @@
         <v>108</v>
       </c>
       <c r="V16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W16" t="s">
         <v>108</v>
@@ -4265,10 +4214,10 @@
         <v>108</v>
       </c>
       <c r="AB16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD16" t="s">
         <v>108</v>
@@ -4295,25 +4244,25 @@
         <v>108</v>
       </c>
       <c r="AL16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS16" t="s">
         <v>108</v>
@@ -4325,7 +4274,7 @@
         <v>108</v>
       </c>
       <c r="AV16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW16" t="s">
         <v>108</v>
@@ -4400,13 +4349,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV16" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW16" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4471,10 +4420,10 @@
         <v>108</v>
       </c>
       <c r="U17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W17" t="s">
         <v>108</v>
@@ -4492,10 +4441,10 @@
         <v>108</v>
       </c>
       <c r="AB17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD17" t="s">
         <v>108</v>
@@ -4525,34 +4474,34 @@
         <v>108</v>
       </c>
       <c r="AM17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW17" t="s">
         <v>108</v>
@@ -4627,13 +4576,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BW17" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4701,7 +4650,7 @@
         <v>108</v>
       </c>
       <c r="V18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W18" t="s">
         <v>108</v>
@@ -4719,13 +4668,13 @@
         <v>108</v>
       </c>
       <c r="AB18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE18" t="s">
         <v>108</v>
@@ -4749,37 +4698,37 @@
         <v>108</v>
       </c>
       <c r="AL18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW18" t="s">
         <v>108</v>
@@ -4854,13 +4803,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BV18" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW18" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4928,7 +4877,7 @@
         <v>108</v>
       </c>
       <c r="V19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W19" t="s">
         <v>108</v>
@@ -4946,16 +4895,16 @@
         <v>108</v>
       </c>
       <c r="AB19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF19" t="s">
         <v>108</v>
@@ -4988,22 +4937,22 @@
         <v>108</v>
       </c>
       <c r="AP19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV19" t="s">
         <v>108</v>
@@ -5081,13 +5030,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV19" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW19" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5209,19 +5158,19 @@
         <v>108</v>
       </c>
       <c r="AN20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS20" t="s">
         <v>108</v>
@@ -5308,13 +5257,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BV20" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5379,10 +5328,10 @@
         <v>108</v>
       </c>
       <c r="U21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W21" t="s">
         <v>108</v>
@@ -5400,13 +5349,13 @@
         <v>108</v>
       </c>
       <c r="AB21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE21" t="s">
         <v>108</v>
@@ -5442,16 +5391,16 @@
         <v>108</v>
       </c>
       <c r="AP21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT21" t="s">
         <v>108</v>
@@ -5535,13 +5484,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV21" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW21" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5609,7 +5558,7 @@
         <v>108</v>
       </c>
       <c r="V22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W22" t="s">
         <v>108</v>
@@ -5630,13 +5579,13 @@
         <v>108</v>
       </c>
       <c r="AC22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF22" t="s">
         <v>108</v>
@@ -5660,34 +5609,34 @@
         <v>108</v>
       </c>
       <c r="AM22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW22" t="s">
         <v>108</v>
@@ -5762,13 +5711,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BV22" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW22" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5854,13 +5803,13 @@
         <v>108</v>
       </c>
       <c r="AB23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE23" t="s">
         <v>108</v>
@@ -5884,37 +5833,37 @@
         <v>108</v>
       </c>
       <c r="AL23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT23" t="s">
         <v>108</v>
       </c>
       <c r="AU23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW23" t="s">
         <v>108</v>
@@ -5989,13 +5938,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV23" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW23" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6063,7 +6012,7 @@
         <v>108</v>
       </c>
       <c r="V24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W24" t="s">
         <v>108</v>
@@ -6081,7 +6030,7 @@
         <v>108</v>
       </c>
       <c r="AB24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC24" t="s">
         <v>108</v>
@@ -6120,28 +6069,28 @@
         <v>108</v>
       </c>
       <c r="AO24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW24" t="s">
         <v>108</v>
@@ -6216,13 +6165,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV24" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW24" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6308,10 +6257,10 @@
         <v>108</v>
       </c>
       <c r="AB25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD25" t="s">
         <v>108</v>
@@ -6338,25 +6287,25 @@
         <v>108</v>
       </c>
       <c r="AL25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS25" t="s">
         <v>108</v>
@@ -6443,13 +6392,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV25" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW25" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6670,13 +6619,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV26" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW26" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6744,7 +6693,7 @@
         <v>108</v>
       </c>
       <c r="V27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W27" t="s">
         <v>108</v>
@@ -6762,16 +6711,16 @@
         <v>108</v>
       </c>
       <c r="AB27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF27" t="s">
         <v>108</v>
@@ -6792,25 +6741,25 @@
         <v>108</v>
       </c>
       <c r="AL27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS27" t="s">
         <v>108</v>
@@ -6897,13 +6846,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV27" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW27" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -6992,13 +6941,13 @@
         <v>108</v>
       </c>
       <c r="AC28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF28" t="s">
         <v>108</v>
@@ -7022,34 +6971,34 @@
         <v>108</v>
       </c>
       <c r="AM28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW28" t="s">
         <v>108</v>
@@ -7124,13 +7073,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV28" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW28" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7249,22 +7198,22 @@
         <v>108</v>
       </c>
       <c r="AM29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS29" t="s">
         <v>108</v>
@@ -7351,13 +7300,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV29" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW29" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7440,13 +7389,13 @@
         <v>108</v>
       </c>
       <c r="AA30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD30" t="s">
         <v>108</v>
@@ -7473,19 +7422,19 @@
         <v>108</v>
       </c>
       <c r="AL30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ30" t="s">
         <v>108</v>
@@ -7578,13 +7527,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV30" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW30" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7676,7 +7625,7 @@
         <v>108</v>
       </c>
       <c r="AD31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE31" t="s">
         <v>108</v>
@@ -7700,25 +7649,25 @@
         <v>108</v>
       </c>
       <c r="AL31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN31" t="s">
         <v>108</v>
       </c>
       <c r="AO31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS31" t="s">
         <v>108</v>
@@ -7805,13 +7754,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BV31" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW31" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7927,22 +7876,22 @@
         <v>108</v>
       </c>
       <c r="AL32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR32" t="s">
         <v>108</v>
@@ -8032,13 +7981,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BV32" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW32" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8124,10 +8073,10 @@
         <v>108</v>
       </c>
       <c r="AB33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD33" t="s">
         <v>108</v>
@@ -8154,28 +8103,28 @@
         <v>108</v>
       </c>
       <c r="AL33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT33" t="s">
         <v>108</v>
@@ -8184,10 +8133,10 @@
         <v>108</v>
       </c>
       <c r="AV33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX33" t="s">
         <v>108</v>
@@ -8259,13 +8208,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV33" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW33" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8333,7 +8282,7 @@
         <v>108</v>
       </c>
       <c r="V34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W34" t="s">
         <v>108</v>
@@ -8351,10 +8300,10 @@
         <v>108</v>
       </c>
       <c r="AB34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD34" t="s">
         <v>108</v>
@@ -8381,37 +8330,37 @@
         <v>108</v>
       </c>
       <c r="AL34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR34" t="s">
         <v>108</v>
       </c>
       <c r="AS34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT34" t="s">
         <v>108</v>
       </c>
       <c r="AU34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW34" t="s">
         <v>108</v>
@@ -8486,13 +8435,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV34" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW34" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sugar_tukey_classification_matrix.xlsx
+++ b/outputs/Sugar_tukey_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
